--- a/AAII_Financials/Yearly/AIRYY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/AIRYY_YR_FIN.xlsx
@@ -2303,10 +2303,10 @@
         <v>54</v>
       </c>
       <c r="D62" s="3">
-        <v>3107000</v>
+        <v>3131100</v>
       </c>
       <c r="E62" s="3">
-        <v>1599000</v>
+        <v>1624600</v>
       </c>
       <c r="F62" s="3">
         <v>2604400</v>
